--- a/candidates/2026-08-24.xlsx
+++ b/candidates/2026-08-24.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidates'!$A$1:$J$1</definedName>
@@ -852,12 +853,12 @@
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Judge allows Trump’s mail-in ballots plan to proceed, for now</t>
+          <t>8/26: The Takeout with Major Garrett</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NBC News</t>
+          <t>CBS News</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -867,7 +868,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/elections/judge-allows-trumps-mail-ballots-plan-proceed-least-now-rcna594365</t>
+          <t>https://www.cbsnews.com/video/082626-the-takeout-with-major-garrett/</t>
         </is>
       </c>
       <c r="F11" s="2" t="n"/>
@@ -888,12 +889,12 @@
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>8/26: The Takeout with Major Garrett</t>
+          <t>A federal prisoner with no clear ties to Alaska advances in primary for the state's US House seat</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CBS News</t>
+          <t>ABC News</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -903,7 +904,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/video/082626-the-takeout-with-major-garrett/</t>
+          <t>https://abcnews.com/Politics/wireStory/federal-prisoner-clear-ties-alaska-advances-primary-states-135988370</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
@@ -924,7 +925,7 @@
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>A federal prisoner with no clear ties to Alaska advances in primary for the state's US House seat</t>
+          <t>Democratic states file new lawsuit seeking to block Trump’s order limiting mail voting in midterms</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -939,7 +940,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/federal-prisoner-clear-ties-alaska-advances-primary-states-135988370</t>
+          <t>https://abcnews.com/Politics/wireStory/democratic-states-file-new-lawsuit-seeking-block-trumps-135974009</t>
         </is>
       </c>
       <c r="F13" s="2" t="n"/>
@@ -960,7 +961,7 @@
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Democratic states file new lawsuit seeking to block Trump’s order limiting mail voting in midterms</t>
+          <t>Republican with same name as incumbent Dan Sullivan advances from Alaska US Senate primary</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -975,7 +976,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/democratic-states-file-new-lawsuit-seeking-block-trumps-135974009</t>
+          <t>https://abcnews.com/Politics/wireStory/republican-same-incumbent-dan-sullivan-advances-alaska-us-135960450</t>
         </is>
       </c>
       <c r="F14" s="2" t="n"/>
@@ -996,7 +997,7 @@
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Republican with same name as incumbent Dan Sullivan advances from Alaska US Senate primary</t>
+          <t>Republican Daniel Sullivan advances to the general election for U.S. Senate in Alaska</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1011,7 +1012,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/republican-same-incumbent-dan-sullivan-advances-alaska-us-135960450</t>
+          <t>https://abcnews.com/Politics/wireStory/republican-daniel-sullivan-advances-general-election-us-senate-135960000</t>
         </is>
       </c>
       <c r="F15" s="2" t="n"/>
@@ -1032,22 +1033,22 @@
       <c r="A16" s="2" t="n"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Republican Daniel Sullivan advances to the general election for U.S. Senate in Alaska</t>
+          <t>Judge hits DOJ lawyers with barrage of questions on Kennedy Center changes</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ABC News</t>
+          <t>NBC News</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Aug 26, 2026</t>
+          <t>Aug 27, 2026</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/republican-daniel-sullivan-advances-general-election-us-senate-135960000</t>
+          <t>https://www.nbcnews.com/politics/trump-administration/kennedy-center-hearing-judge-presses-doj-lawyers-renovation-renaming-rcna594707</t>
         </is>
       </c>
       <c r="F16" s="2" t="n"/>
@@ -1060,7 +1061,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Aug 26</t>
+          <t>Aug 27</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1069,7 @@
       <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Judge hits DOJ lawyers with barrage of questions on Kennedy Center changes</t>
+          <t>Trump signs executive order to rename Lake Ontario as ‘Lake America’</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1083,7 +1084,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/trump-administration/kennedy-center-hearing-judge-presses-doj-lawyers-renovation-renaming-rcna594707</t>
+          <t>https://www.nbcnews.com/politics/trump-administration/trump-orders-lake-ontario-renamed-lake-america-canada-trade-war-rcna594750</t>
         </is>
       </c>
       <c r="F17" s="2" t="n"/>
@@ -1104,7 +1105,7 @@
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Trump signs executive order to rename Lake Ontario as ‘Lake America’</t>
+          <t>Wyoming’s Republican governor raises concerns over ‘aggressive’ DOJ election monitors</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1119,7 +1120,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/trump-administration/trump-orders-lake-ontario-renamed-lake-america-canada-trade-war-rcna594750</t>
+          <t>https://www.nbcnews.com/politics/2026-election/wyoming-republican-governor-concerns-aggressive-doj-election-monitors-rcna594730</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
@@ -1140,7 +1141,7 @@
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Wyoming’s Republican governor raises concerns over ‘aggressive’ DOJ election monitors</t>
+          <t>Secret Service officials placed on leave in inquiry over ‘potential misconduct’</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1155,7 +1156,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/2026-election/wyoming-republican-governor-concerns-aggressive-doj-election-monitors-rcna594730</t>
+          <t>https://www.nbcnews.com/politics/white-house/secret-service-officials-placed-leave-inquiry-potential-misconduct-rcna594630</t>
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
@@ -1176,12 +1177,12 @@
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Secret Service officials placed on leave in inquiry over ‘potential misconduct’</t>
+          <t>8/27: The Takeout with Major Garrett</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NBC News</t>
+          <t>CBS News</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1191,7 +1192,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/white-house/secret-service-officials-placed-leave-inquiry-potential-misconduct-rcna594630</t>
+          <t>https://www.cbsnews.com/video/082726-the-takeout-with-major-garrett/</t>
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
@@ -1212,12 +1213,12 @@
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>8/27: The Takeout with Major Garrett</t>
+          <t>Group of Democratic senators calls on ICE to cancel plan to buy electric shock gloves</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CBS News</t>
+          <t>ABC News</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1227,7 +1228,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/video/082726-the-takeout-with-major-garrett/</t>
+          <t>https://abcnews.com/Politics/wireStory/group-democratic-senators-calls-ice-cancel-plan-buy-136008188</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
@@ -1248,7 +1249,7 @@
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Group of Democratic senators calls on ICE to cancel plan to buy electric shock gloves</t>
+          <t>Republicans face midterm verdict as Iran war drags on longer than Trump promised</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1263,7 +1264,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/group-democratic-senators-calls-ice-cancel-plan-buy-136008188</t>
+          <t>https://abcnews.com/Politics/wireStory/republicans-face-midterm-verdict-iran-war-drags-months-135998199</t>
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
@@ -1284,7 +1285,7 @@
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Republicans face midterm verdict as Iran war drags on longer than Trump promised</t>
+          <t>US goals have shifted after 6 months of Iran war. The Strait of Hormuz is now a top concern</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1299,7 +1300,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/republicans-face-midterm-verdict-iran-war-drags-months-135998199</t>
+          <t>https://abcnews.com/Politics/wireStory/us-goals-shifted-after-6-months-iran-war-135995683</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -1320,7 +1321,7 @@
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>US goals have shifted after 6 months of Iran war. The Strait of Hormuz is now a top concern</t>
+          <t>Tate brothers' extradition fight back in Miami court as brothers seek release on bond</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1335,7 +1336,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/us-goals-shifted-after-6-months-iran-war-135995683</t>
+          <t>https://abcnews.com/Politics/wireStory/tate-brothers-extradition-fight-back-miami-court-brothers-135995466</t>
         </is>
       </c>
       <c r="F24" s="2" t="n"/>
@@ -1356,12 +1357,12 @@
       <c r="A25" s="2" t="n"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Tate brothers' extradition fight back in Miami court as brothers seek release on bond</t>
+          <t>Latvia's foreign minister warns of Russian sabotage acts in Europe</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ABC News</t>
+          <t>PBS NewsHour</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1371,7 +1372,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/tate-brothers-extradition-fight-back-miami-court-brothers-135995466</t>
+          <t>https://www.pbs.org/newshour/show/latvias-foreign-minister-warns-of-russian-sabotage-acts-on-europe</t>
         </is>
       </c>
       <c r="F25" s="2" t="n"/>
@@ -1392,7 +1393,7 @@
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Latvia's foreign minister warns of Russian sabotage acts in Europe</t>
+          <t>Jan. 6 rioters pursue new path for payments from Trump administration</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1407,7 +1408,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/show/latvias-foreign-minister-warns-of-russian-sabotage-acts-on-europe</t>
+          <t>https://www.pbs.org/newshour/show/jan-6-rioters-pursue-new-path-for-payments-from-trump-administration</t>
         </is>
       </c>
       <c r="F26" s="2" t="n"/>
@@ -1428,7 +1429,7 @@
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Jan. 6 rioters pursue new path for payments from Trump administration</t>
+          <t>Gaza's traumatized youth search for glimmers of hope in devastated homeland</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1443,7 +1444,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/show/jan-6-rioters-pursue-new-path-for-payments-from-trump-administration</t>
+          <t>https://www.pbs.org/newshour/show/gazas-traumatized-youth-search-for-glimmers-of-hope-in-devastated-homeland</t>
         </is>
       </c>
       <c r="F27" s="2" t="n"/>
@@ -1464,22 +1465,22 @@
       <c r="A28" s="2" t="n"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Gaza's traumatized youth search for glimmers of hope in devastated homeland</t>
+          <t>Trump signs order renaming Lake Ontario to Lake America</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>PBS NewsHour</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Aug 27, 2026</t>
+          <t>Aug 28, 2026</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/show/gazas-traumatized-youth-search-for-glimmers-of-hope-in-devastated-homeland</t>
+          <t>https://www.npr.org/2026/08/28/nx-s1-5946811/trump-signs-order-renaming-lake-ontario-to-lake-america</t>
         </is>
       </c>
       <c r="F28" s="2" t="n"/>
@@ -1492,7 +1493,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Aug 27</t>
+          <t>Aug 28</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1501,7 @@
       <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Trump signs order renaming Lake Ontario to Lake America</t>
+          <t>How Democrats in Congress are preparing for Trump midterm election interference</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1515,7 +1516,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://www.npr.org/2026/08/28/nx-s1-5946811/trump-signs-order-renaming-lake-ontario-to-lake-america</t>
+          <t>https://www.npr.org/2026/08/28/nx-s1-5940881/democrats-congress-midterm-elections-trump</t>
         </is>
       </c>
       <c r="F29" s="2" t="n"/>
@@ -1536,7 +1537,7 @@
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>How Democrats in Congress are preparing for Trump midterm election interference</t>
+          <t>Trump administration proposal would allow federal grants to be terminated on a whim</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1551,7 +1552,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>https://www.npr.org/2026/08/28/nx-s1-5940881/democrats-congress-midterm-elections-trump</t>
+          <t>https://www.npr.org/2026/08/28/nx-s1-5943238/trump-administration-proposal-would-allow-federal-grants-to-be-terminated-on-a-whim</t>
         </is>
       </c>
       <c r="F30" s="2" t="n"/>
@@ -1572,12 +1573,12 @@
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Trump administration proposal would allow federal grants to be terminated on a whim</t>
+          <t>Trump says U.S. has struck deal with Venezuela to take control of 65 billion barrels of oil reserves</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>NBC News</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1587,7 +1588,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>https://www.npr.org/2026/08/28/nx-s1-5943238/trump-administration-proposal-would-allow-federal-grants-to-be-terminated-on-a-whim</t>
+          <t>https://www.nbcnews.com/world/venezuela/us-entered-deal-venezuela-take-control-65-billion-barrels-oil-reserves-rcna594966</t>
         </is>
       </c>
       <c r="F31" s="2" t="n"/>
@@ -1608,7 +1609,7 @@
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Trump says U.S. has struck deal with Venezuela to take control of 65 billion barrels of oil reserves</t>
+          <t>Elon Musk enters the midterm chat: From the Politics Desk</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1623,7 +1624,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/world/venezuela/us-entered-deal-venezuela-take-control-65-billion-barrels-oil-reserves-rcna594966</t>
+          <t>https://www.nbcnews.com/politics/politics-news/elon-musk-enters-midterm-chat-politics-desk-rcna594934</t>
         </is>
       </c>
       <c r="F32" s="2" t="n"/>
@@ -1644,7 +1645,7 @@
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Elon Musk enters the midterm chat: From the Politics Desk</t>
+          <t>Trump signs order to create space-focused military academy</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1659,7 +1660,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/politics-news/elon-musk-enters-midterm-chat-politics-desk-rcna594934</t>
+          <t>https://www.nbcnews.com/politics/trump-administration/trump-space-academy-nasa-military-rcna594870</t>
         </is>
       </c>
       <c r="F33" s="2" t="n"/>
@@ -1680,7 +1681,7 @@
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Trump signs order to create space-focused military academy</t>
+          <t>Judge blocks Trump’s Postal Service regulation on mail-in ballots</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1695,7 +1696,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/trump-administration/trump-space-academy-nasa-military-rcna594870</t>
+          <t>https://www.nbcnews.com/politics/2026-election/judge-blocks-trumps-postal-service-regulation-mail-ballots-rcna594692</t>
         </is>
       </c>
       <c r="F34" s="2" t="n"/>
@@ -1716,12 +1717,12 @@
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Judge blocks Trump’s Postal Service regulation on mail-in ballots</t>
+          <t>Dolly Parton was the polar opposite of our bullying president | Robert Reich</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>NBC News</t>
+          <t>The Guardian</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1731,7 +1732,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>https://www.nbcnews.com/politics/2026-election/judge-blocks-trumps-postal-service-regulation-mail-ballots-rcna594692</t>
+          <t>https://www.theguardian.com/commentisfree/2026/aug/28/dolly-parton-trump-canada</t>
         </is>
       </c>
       <c r="F35" s="2" t="n"/>
@@ -1752,7 +1753,7 @@
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Dolly Parton was the polar opposite of our bullying president | Robert Reich</t>
+          <t>How did Trump get so rich? | Politics Weekly America</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1767,7 +1768,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/commentisfree/2026/aug/28/dolly-parton-trump-canada</t>
+          <t>https://www.theguardian.com/politics/video/2026/aug/27/how-did-trump-get-so-rich-politics-weekly-america</t>
         </is>
       </c>
       <c r="F36" s="2" t="n"/>
@@ -1788,12 +1789,12 @@
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>How did Trump get so rich? | Politics Weekly America</t>
+          <t>Milo Yiannopoulos is in ICE custody facing a final removal order, sources say</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>The Guardian</t>
+          <t>CBS News</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1803,7 +1804,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/politics/video/2026/aug/27/how-did-trump-get-so-rich-politics-weekly-america</t>
+          <t>https://www.cbsnews.com/news/milo-yiannopoulos-ice-custody-agency-records/</t>
         </is>
       </c>
       <c r="F37" s="2" t="n"/>
@@ -1824,7 +1825,7 @@
       <c r="A38" s="2" t="n"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Milo Yiannopoulos is in ICE custody facing a final removal order, sources say</t>
+          <t>ICE arrests right-wing commentator Milo Yiannopoulos, labels him an "illegal alien"</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1839,7 +1840,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/news/milo-yiannopoulos-ice-custody-agency-records/</t>
+          <t>https://www.cbsnews.com/video/ice-arrests-right-wing-commentator-milo-yiannopoulos-labels-him-an-illegal-alien/</t>
         </is>
       </c>
       <c r="F38" s="2" t="n"/>
@@ -1860,7 +1861,7 @@
       <c r="A39" s="2" t="n"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ICE arrests right-wing commentator Milo Yiannopoulos, labels him an "illegal alien"</t>
+          <t>Trump signs executive order to create a U.S. Space Academy</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1875,7 +1876,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/video/ice-arrests-right-wing-commentator-milo-yiannopoulos-labels-him-an-illegal-alien/</t>
+          <t>https://www.cbsnews.com/news/trump-signs-executive-order-to-create-a-us-space-academy/</t>
         </is>
       </c>
       <c r="F39" s="2" t="n"/>
@@ -1896,7 +1897,7 @@
       <c r="A40" s="2" t="n"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Trump signs executive order to create a U.S. Space Academy</t>
+          <t>8/28: CBS Evening News</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1911,7 +1912,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/news/trump-signs-executive-order-to-create-a-us-space-academy/</t>
+          <t>https://www.cbsnews.com/video/082826-cbs-evening-news/</t>
         </is>
       </c>
       <c r="F40" s="2" t="n"/>
@@ -1932,7 +1933,7 @@
       <c r="A41" s="2" t="n"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>8/28: CBS Evening News</t>
+          <t>Judge again rejects Trump's bid to erase his New York hush money conviction</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1947,7 +1948,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/video/082826-cbs-evening-news/</t>
+          <t>https://www.cbsnews.com/news/trump-hush-money-immunity-bid-again-rejected/</t>
         </is>
       </c>
       <c r="F41" s="2" t="n"/>
@@ -1968,7 +1969,7 @@
       <c r="A42" s="2" t="n"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Judge again rejects Trump's bid to erase his New York hush money conviction</t>
+          <t>Trump says he'll visit Pentagon, not NYC, to mark 25 years since 9/11</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1983,7 +1984,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/news/trump-hush-money-immunity-bid-again-rejected/</t>
+          <t>https://www.cbsnews.com/news/trump-september-11-plans-new-york-pentagon/</t>
         </is>
       </c>
       <c r="F42" s="2" t="n"/>
@@ -2004,7 +2005,7 @@
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Trump says he'll visit Pentagon, not NYC, to mark 25 years since 9/11</t>
+          <t>At FBI, history of hiring prostitutes may not be employment barrier</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2019,7 +2020,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/news/trump-september-11-plans-new-york-pentagon/</t>
+          <t>https://www.cbsnews.com/news/fbi-candidates-prostitutes-theft/</t>
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
@@ -2040,7 +2041,7 @@
       <c r="A44" s="2" t="n"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>At FBI, history of hiring prostitutes may not be employment barrier</t>
+          <t>Judge temporarily blocks new Postal Service rules for mail voting</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2055,7 +2056,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/news/fbi-candidates-prostitutes-theft/</t>
+          <t>https://www.cbsnews.com/news/judge-temporarily-blocks-new-postal-service-rules-for-mail-voting-trump/</t>
         </is>
       </c>
       <c r="F44" s="2" t="n"/>
@@ -2076,12 +2077,12 @@
       <c r="A45" s="2" t="n"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Judge temporarily blocks new Postal Service rules for mail voting</t>
+          <t>Wyoming governor requests investigation into activity of DOJ monitors during primary</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CBS News</t>
+          <t>ABC News</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2091,7 +2092,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>https://www.cbsnews.com/news/judge-temporarily-blocks-new-postal-service-rules-for-mail-voting-trump/</t>
+          <t>https://abcnews.com/Politics/wireStory/wyoming-governor-requests-investigation-activity-justice-department-monitors-136040978</t>
         </is>
       </c>
       <c r="F45" s="2" t="n"/>
@@ -2112,7 +2113,7 @@
       <c r="A46" s="2" t="n"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Wyoming governor requests investigation into activity of DOJ monitors during primary</t>
+          <t>Civil rights groups make urgent plea for voting rights</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2127,7 +2128,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/wyoming-governor-requests-investigation-activity-justice-department-monitors-136040978</t>
+          <t>https://abcnews.com/Politics/wireStory/civil-rights-groups-make-urgent-plea-voting-rights-136021736</t>
         </is>
       </c>
       <c r="F46" s="2" t="n"/>
@@ -2148,7 +2149,7 @@
       <c r="A47" s="2" t="n"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Civil rights groups make urgent plea for voting rights</t>
+          <t>Judge again blocks Trump mail ballot executive order in ruling that’s likely to be swiftly appealed</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2163,7 +2164,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/civil-rights-groups-make-urgent-plea-voting-rights-136021736</t>
+          <t>https://abcnews.com/Politics/wireStory/judge-blocks-trump-mail-ballot-executive-order-ruling-136019938</t>
         </is>
       </c>
       <c r="F47" s="2" t="n"/>
@@ -2184,7 +2185,7 @@
       <c r="A48" s="2" t="n"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Judge again blocks Trump mail ballot executive order in ruling that’s likely to be swiftly appealed</t>
+          <t>As midterms approach, Republican candidates weigh how closely to align with Trump</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2199,7 +2200,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/judge-blocks-trump-mail-ballot-executive-order-ruling-136019938</t>
+          <t>https://abcnews.com/Politics/wireStory/midterm-elections-approach-republican-candidates-weigh-closely-align-136013650</t>
         </is>
       </c>
       <c r="F48" s="2" t="n"/>
@@ -2220,12 +2221,12 @@
       <c r="A49" s="2" t="n"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>As midterms approach, Republican candidates weigh how closely to align with Trump</t>
+          <t>Trump says U.S. has entered deal with Venezuela to control 65 billion barrels of its oil reserves</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>ABC News</t>
+          <t>PBS NewsHour</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2235,7 +2236,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>https://abcnews.com/Politics/wireStory/midterm-elections-approach-republican-candidates-weigh-closely-align-136013650</t>
+          <t>https://www.pbs.org/newshour/politics/trump-says-u-s-has-entered-deal-with-venezuela-to-control-65-billion-barrels-of-its-oil-reserves</t>
         </is>
       </c>
       <c r="F49" s="2" t="n"/>
@@ -2256,7 +2257,7 @@
       <c r="A50" s="2" t="n"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Trump says U.S. has entered deal with Venezuela to control 65 billion barrels of its oil reserves</t>
+          <t>News Wrap: Friday marks 6 months since Iran war started</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2271,7 +2272,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/politics/trump-says-u-s-has-entered-deal-with-venezuela-to-control-65-billion-barrels-of-its-oil-reserves</t>
+          <t>https://www.pbs.org/newshour/show/news-wrap-friday-marks-6-months-since-iran-war-started</t>
         </is>
       </c>
       <c r="F50" s="2" t="n"/>
@@ -2292,7 +2293,7 @@
       <c r="A51" s="2" t="n"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>News Wrap: Friday marks 6 months since Iran war started</t>
+          <t>Fed Chair Warsh not ruling out interest rate hike amid inflation concerns</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2307,7 +2308,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/show/news-wrap-friday-marks-6-months-since-iran-war-started</t>
+          <t>https://www.pbs.org/newshour/show/fed-chair-warsh-not-ruling-out-interest-rate-hike-amid-inflation-concerns</t>
         </is>
       </c>
       <c r="F51" s="2" t="n"/>
@@ -2328,7 +2329,7 @@
       <c r="A52" s="2" t="n"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fed Chair Warsh not ruling out interest rate hike amid inflation concerns</t>
+          <t>National parks under strain from Trump's construction projects and political pressure</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2343,7 +2344,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/show/fed-chair-warsh-not-ruling-out-interest-rate-hike-amid-inflation-concerns</t>
+          <t>https://www.pbs.org/newshour/show/national-parks-under-strain-from-trumps-construction-projects-and-political-pressure</t>
         </is>
       </c>
       <c r="F52" s="2" t="n"/>
@@ -2364,7 +2365,7 @@
       <c r="A53" s="2" t="n"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>National parks under strain from Trump's construction projects and political pressure</t>
+          <t>Brooks and Capehart on Trump's 'forever trade war'</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2379,7 +2380,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/show/national-parks-under-strain-from-trumps-construction-projects-and-political-pressure</t>
+          <t>https://www.pbs.org/newshour/show/brooks-and-capehart-on-trumps-forever-trade-war</t>
         </is>
       </c>
       <c r="F53" s="2" t="n"/>
@@ -2400,7 +2401,7 @@
       <c r="A54" s="2" t="n"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Brooks and Capehart on Trump's 'forever trade war'</t>
+          <t>National Park Service backs Trump's arch, despite its impact on key Washington sightlines</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2415,7 +2416,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/show/brooks-and-capehart-on-trumps-forever-trade-war</t>
+          <t>https://www.pbs.org/newshour/politics/national-park-service-backs-trumps-arch-despite-its-impact-on-key-washington-sightlines</t>
         </is>
       </c>
       <c r="F54" s="2" t="n"/>
@@ -2436,7 +2437,7 @@
       <c r="A55" s="2" t="n"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>National Park Service backs Trump's arch, despite its impact on key Washington sightlines</t>
+          <t>U.S. targets Egyptian bank's UAE branches under new push for Iran's economic isolation</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -2451,7 +2452,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/politics/national-park-service-backs-trumps-arch-despite-its-impact-on-key-washington-sightlines</t>
+          <t>https://www.pbs.org/newshour/world/u-s-targets-egyptian-banks-uae-branches-under-new-push-for-irans-economic-isolation</t>
         </is>
       </c>
       <c r="F55" s="2" t="n"/>
@@ -2472,7 +2473,7 @@
       <c r="A56" s="2" t="n"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>U.S. targets Egyptian bank's UAE branches under new push for Iran's economic isolation</t>
+          <t>Trump loses again in bid to erase his hush money conviction</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -2487,7 +2488,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/world/u-s-targets-egyptian-banks-uae-branches-under-new-push-for-irans-economic-isolation</t>
+          <t>https://www.pbs.org/newshour/politics/trump-loses-again-in-bid-to-erase-his-hush-money-conviction</t>
         </is>
       </c>
       <c r="F56" s="2" t="n"/>
@@ -2508,7 +2509,7 @@
       <c r="A57" s="2" t="n"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Trump loses again in bid to erase his hush money conviction</t>
+          <t>Judge says Pentagon's measures against Anthropic were 'illegal and baseless'</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -2523,7 +2524,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/politics/trump-loses-again-in-bid-to-erase-his-hush-money-conviction</t>
+          <t>https://www.pbs.org/newshour/politics/judge-says-pentagons-measures-against-anthropic-were-illegal-and-baseless</t>
         </is>
       </c>
       <c r="F57" s="2" t="n"/>
@@ -2544,7 +2545,7 @@
       <c r="A58" s="2" t="n"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Judge says Pentagon's measures against Anthropic were 'illegal and baseless'</t>
+          <t>Judge again blocks Trump mail ballot executive order in ruling that's likely to be swiftly appealed</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -2559,7 +2560,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/politics/judge-says-pentagons-measures-against-anthropic-were-illegal-and-baseless</t>
+          <t>https://www.pbs.org/newshour/politics/judge-again-blocks-trump-mail-ballot-executive-order-in-ruling-thats-likely-to-be-swiftly-appealed</t>
         </is>
       </c>
       <c r="F58" s="2" t="n"/>
@@ -2580,7 +2581,7 @@
       <c r="A59" s="2" t="n"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Judge again blocks Trump mail ballot executive order in ruling that's likely to be swiftly appealed</t>
+          <t>WATCH: Trump bestows Artemis II crew with Congressional Space Medal of Honor</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -2595,7 +2596,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/politics/judge-again-blocks-trump-mail-ballot-executive-order-in-ruling-thats-likely-to-be-swiftly-appealed</t>
+          <t>https://www.pbs.org/newshour/politics/watch-live-trump-bestows-artemis-ii-crew-with-congressional-space-medal-of-honor</t>
         </is>
       </c>
       <c r="F59" s="2" t="n"/>
@@ -2616,7 +2617,7 @@
       <c r="A60" s="2" t="n"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>WATCH: Trump bestows Artemis II crew with Congressional Space Medal of Honor</t>
+          <t>WATCH: March on Washington rally draws attention to voting rights with Jeffries, Sanders</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -2631,7 +2632,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/politics/watch-live-trump-bestows-artemis-ii-crew-with-congressional-space-medal-of-honor</t>
+          <t>https://www.pbs.org/newshour/politics/watch-live-march-on-washington-rally-draws-attention-to-voting-rights-with-jeffries-sanders</t>
         </is>
       </c>
       <c r="F60" s="2" t="n"/>
@@ -2652,22 +2653,22 @@
       <c r="A61" s="2" t="n"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>WATCH: March on Washington rally draws attention to voting rights with Jeffries, Sanders</t>
+          <t>Week in Politics: Trump renames Lake Ontario 'Lake America'; Fed chair signals hikes</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>PBS NewsHour</t>
+          <t>NPR</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Aug 28, 2026</t>
+          <t>Aug 29, 2026</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>https://www.pbs.org/newshour/politics/watch-live-march-on-washington-rally-draws-attention-to-voting-rights-with-jeffries-sanders</t>
+          <t>https://www.npr.org/2026/08/29/nx-s1-5945108/week-in-politics-trump-renames-lake-ontario-lake-america-fed-chair-signals-hikes</t>
         </is>
       </c>
       <c r="F61" s="2" t="n"/>
@@ -2680,7 +2681,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Aug 28</t>
+          <t>Aug 29</t>
         </is>
       </c>
     </row>
@@ -2691,9 +2692,12 @@
       <formula>LOWER($A2)="y"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="A2:A61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"y,n"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lists!$A$1:$A$17</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -2760,4 +2764,137 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Civil Liberties</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Civil Rights &amp; Minorities</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Courts &amp; SCOTUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Democracy &amp; Rule of Law</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Economy &amp; Tariffs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Environment &amp; Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Executive Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Federal Workforce</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Foreign Policy &amp; Aid</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Immigration</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Immigration / Free Speech</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LGBTQ+ Rights</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Press Freedom</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Public Health</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Women's Rights / LGBTQ+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>